--- a/task264/golden/levy_apportionment_2027-28.xlsx
+++ b/task264/golden/levy_apportionment_2027-28.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>Member council</t>
   </si>
@@ -105,16 +105,19 @@
     <t>Levy 2025-26 invoiced (GBP)</t>
   </si>
   <si>
-    <t>Paid by 31 March 2026 (GBP)</t>
-  </si>
-  <si>
-    <t>Still owed on 31 March 2026 (GBP)</t>
+    <t>Paid by the instalments' due dates (GBP)</t>
+  </si>
+  <si>
+    <t>Paid after the due date, by 31 March 2026 (GBP)</t>
+  </si>
+  <si>
+    <t>Unpaid on 31 March 2026 (GBP)</t>
   </si>
   <si>
     <t>Prepared by Finance for the Authority's meeting of 21 January 2027 (item 7). Figures from the 2025-26 visitor survey (both waves and the contractor's weights), the car-park systems and the finance system as exported on 6 January 2027.</t>
   </si>
   <si>
-    <t>Residents. Resolution 14/2026 counts each member council's residents aged 16 and over who visited at least once between 1 April 2025 and 31 March 2026, each once. The survey interviewed adults leaving the parks, every eighth adult crossing the survey line, so each adult's chance of being interviewed rises with how often they came. Each interview is counted as its expansion weight (its stratum's estimated adult visits over the stratum's interviews) divided by the respondent's visits to the parks in the last 12 months including that day (Q9), which counts each resident once; summed by the home area the contractor coded. 3,973 of the 4,470 interviews were with residents of the member councils; 473 lived outside them and 24 gave no home that could be placed, and neither is counted (paragraphs 4 and 6).</t>
+    <t>Residents. Resolution 14/2026 counts each member council's residents aged 16 and over who visited at least once between 1 April 2025 and 31 March 2026, each once. The survey interviewed adults leaving the parks, every eighth adult crossing the survey line, so each adult's chance of being interviewed rises with how often they came. Each interview is counted as its expansion weight (its stratum's estimated adult visits over the stratum's interviews) divided by the respondent's visits to the six parks in the last 12 months including that day (Q9, the six parks' answers added, since a resident can be met at any park they visit), which counts each resident once; summed by the home area the contractor coded. 3,973 of the 4,470 interviews were with residents of the member councils; 473 lived outside them and 24 gave no home that could be placed, and neither is counted (paragraphs 4 and 6).</t>
   </si>
   <si>
     <t>Levy. Each council's share of the 7,416,300 pound requirement is its estimated residents over the nine councils' total, unrounded; each levy is rounded to the pound (paragraph 5). Residents are shown to the nearest hundred, and totals are the unrounded estimates added and then rounded, so the rounded figures may not add to them.</t>
@@ -123,7 +126,7 @@
     <t>Car parks. Pay-machine takings are each ticket once (three machines re-sent several days' tickets with a later upload), placed at the park where the machine stood when it took them (PM-2103 stood in Gorthfield's main car park until it replaced PM-2203 at the Water Park on 1 September 2025; its takings to then are at Gorthfield's charges), and divided by 1.2 to take out VAT. The app provider's parking income is stated without VAT and is taken as stated (sessions times charge over 1.2). Vehicles are entries at the car-park counters over the survey year: C-09, the Water Park's loop from 18 August 2025, counts every vehicle in and out, so its counts are halved; C-05 and C-10 both reported Gorthfield's lakeside entrance from 3 to 24 February 2026 and the entrance is counted once; C-07 stood at Thruscote Hall until 14 October 2025, when it moved to Lockshaw Moor's valley car park and C-11 took its place.</t>
   </si>
   <si>
-    <t>Levy collection. Receipts are the 2025-26 levy invoices their references quote, taken on the date the bank credited them (value date); the fourth instalments, due and credited on 31 March 2026, were posted to the cash book on 1 April. The shared finance service's transfers for Hornmere and Wendstow are split by its remittance advices. Chaldale paid its third instalment at its 2024-25 amount.</t>
+    <t>Levy collection. Each receipt counts once against the invoices the cash book allocates it to, each at its own amount where a council's payment run paid a sundry invoice with an instalment (the receipts listing prints the receipt's amount on each of its lines), and is dated by the day the bank credited it (the bank's report, matched on the reference and amount), not the day the finance system posted it: a payment credited on its due date is on time. The fourth instalments credited on 31 March were posted on 1 April, after the cash book's year, and are taken from the bank's report against each payer's open invoice: the shared finance service's transfer pays Hornmere's and Wendstow's, and Ferncote's quoted Grinbury's invoice and is Ferncote's. Chaldale paid its third instalment at its 2024-25 amount; Grinbury's fourth instalment reached the bank on 8 April 2026.</t>
   </si>
 </sst>
 </file>
@@ -532,19 +535,19 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>45800</v>
+        <v>45500</v>
       </c>
       <c r="C2" s="3">
-        <v>0.16859</v>
+        <v>0.168827</v>
       </c>
       <c r="D2" s="2">
-        <v>1250310</v>
+        <v>1252070</v>
       </c>
       <c r="E2" s="2">
         <v>684075</v>
       </c>
       <c r="F2" s="2">
-        <v>566235</v>
+        <v>567995</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -555,16 +558,16 @@
         <v>55900</v>
       </c>
       <c r="C3" s="3">
-        <v>0.205671</v>
+        <v>0.207665</v>
       </c>
       <c r="D3" s="2">
-        <v>1525314</v>
+        <v>1540108</v>
       </c>
       <c r="E3" s="2">
         <v>916786</v>
       </c>
       <c r="F3" s="2">
-        <v>608528</v>
+        <v>623322</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -572,19 +575,19 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>35800</v>
+        <v>35200</v>
       </c>
       <c r="C4" s="3">
-        <v>0.13176</v>
+        <v>0.130653</v>
       </c>
       <c r="D4" s="2">
-        <v>977169</v>
+        <v>968963</v>
       </c>
       <c r="E4" s="2">
         <v>583356</v>
       </c>
       <c r="F4" s="2">
-        <v>393813</v>
+        <v>385607</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -592,19 +595,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>26300</v>
+        <v>26000</v>
       </c>
       <c r="C5" s="3">
-        <v>0.09671100000000001</v>
+        <v>0.096678</v>
       </c>
       <c r="D5" s="2">
-        <v>717236</v>
+        <v>716993</v>
       </c>
       <c r="E5" s="2">
         <v>1132547</v>
       </c>
       <c r="F5" s="2">
-        <v>-415311</v>
+        <v>-415554</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -612,19 +615,19 @@
         <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>27300</v>
+        <v>26900</v>
       </c>
       <c r="C6" s="3">
-        <v>0.100306</v>
+        <v>0.09997399999999999</v>
       </c>
       <c r="D6" s="2">
-        <v>743901</v>
+        <v>741438</v>
       </c>
       <c r="E6" s="2">
         <v>785911</v>
       </c>
       <c r="F6" s="2">
-        <v>-42010</v>
+        <v>-44473</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -632,19 +635,19 @@
         <v>11</v>
       </c>
       <c r="B7" s="2">
-        <v>23800</v>
+        <v>24500</v>
       </c>
       <c r="C7" s="3">
-        <v>0.087663</v>
+        <v>0.091111</v>
       </c>
       <c r="D7" s="2">
-        <v>650135</v>
+        <v>675709</v>
       </c>
       <c r="E7" s="2">
         <v>994247</v>
       </c>
       <c r="F7" s="2">
-        <v>-344112</v>
+        <v>-318538</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -652,19 +655,19 @@
         <v>12</v>
       </c>
       <c r="B8" s="2">
-        <v>20200</v>
+        <v>19900</v>
       </c>
       <c r="C8" s="3">
-        <v>0.074139</v>
+        <v>0.073811</v>
       </c>
       <c r="D8" s="2">
-        <v>549836</v>
+        <v>547403</v>
       </c>
       <c r="E8" s="2">
         <v>528693</v>
       </c>
       <c r="F8" s="2">
-        <v>21143</v>
+        <v>18710</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -672,19 +675,19 @@
         <v>13</v>
       </c>
       <c r="B9" s="2">
-        <v>18800</v>
+        <v>17900</v>
       </c>
       <c r="C9" s="3">
-        <v>0.069215</v>
+        <v>0.066458</v>
       </c>
       <c r="D9" s="2">
-        <v>513321</v>
+        <v>492870</v>
       </c>
       <c r="E9" s="2">
         <v>845501</v>
       </c>
       <c r="F9" s="2">
-        <v>-332180</v>
+        <v>-352631</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -692,19 +695,19 @@
         <v>14</v>
       </c>
       <c r="B10" s="2">
-        <v>17900</v>
+        <v>17500</v>
       </c>
       <c r="C10" s="3">
-        <v>0.065946</v>
+        <v>0.06482300000000001</v>
       </c>
       <c r="D10" s="2">
-        <v>489078</v>
+        <v>480746</v>
       </c>
       <c r="E10" s="2">
         <v>719684</v>
       </c>
       <c r="F10" s="2">
-        <v>-230606</v>
+        <v>-238938</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -712,7 +715,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="5">
-        <v>271900</v>
+        <v>269300</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -733,19 +736,19 @@
         <v>16</v>
       </c>
       <c r="B13" s="2">
-        <v>137600</v>
+        <v>136600</v>
       </c>
       <c r="C13" s="3">
-        <v>0.50602</v>
+        <v>0.507145</v>
       </c>
       <c r="D13" s="2">
-        <v>3752793</v>
+        <v>3761141</v>
       </c>
       <c r="E13" s="2">
         <v>2184217</v>
       </c>
       <c r="F13" s="2">
-        <v>1568576</v>
+        <v>1576924</v>
       </c>
     </row>
   </sheetData>
@@ -874,16 +877,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A167800-18B4-5F7A-AF9B-B8AD1AA592AE}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="44" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -896,8 +900,11 @@
       <c r="D1" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -905,13 +912,16 @@
         <v>664285</v>
       </c>
       <c r="C2" s="2">
-        <v>664285</v>
+        <v>498214</v>
       </c>
       <c r="D2" s="2">
+        <v>166071</v>
+      </c>
+      <c r="E2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -919,13 +929,16 @@
         <v>890351</v>
       </c>
       <c r="C3" s="2">
-        <v>890351</v>
+        <v>667764</v>
       </c>
       <c r="D3" s="2">
+        <v>222587</v>
+      </c>
+      <c r="E3" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -938,8 +951,11 @@
       <c r="D4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -952,8 +968,11 @@
       <c r="D5" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -961,13 +980,16 @@
         <v>763277</v>
       </c>
       <c r="C6" s="2">
-        <v>763277</v>
+        <v>190819</v>
       </c>
       <c r="D6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>381638</v>
+      </c>
+      <c r="E6" s="2">
+        <v>190820</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -975,13 +997,16 @@
         <v>964788</v>
       </c>
       <c r="C7" s="2">
-        <v>964788</v>
+        <v>723591</v>
       </c>
       <c r="D7" s="2">
+        <v>241197</v>
+      </c>
+      <c r="E7" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -989,13 +1014,16 @@
         <v>514387</v>
       </c>
       <c r="C8" s="2">
-        <v>510932</v>
+        <v>382336</v>
       </c>
       <c r="D8" s="2">
+        <v>128596</v>
+      </c>
+      <c r="E8" s="2">
         <v>3455</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1003,13 +1031,16 @@
         <v>821365</v>
       </c>
       <c r="C9" s="2">
-        <v>821365</v>
+        <v>616024</v>
       </c>
       <c r="D9" s="2">
+        <v>205341</v>
+      </c>
+      <c r="E9" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1017,13 +1048,16 @@
         <v>699227</v>
       </c>
       <c r="C10" s="2">
-        <v>699227</v>
+        <v>524421</v>
       </c>
       <c r="D10" s="2">
+        <v>174806</v>
+      </c>
+      <c r="E10" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
@@ -1031,10 +1065,13 @@
         <v>6982400</v>
       </c>
       <c r="C11" s="5">
-        <v>6978945</v>
+        <v>5267889</v>
       </c>
       <c r="D11" s="5">
-        <v>3455</v>
+        <v>1520236</v>
+      </c>
+      <c r="E11" s="5">
+        <v>194275</v>
       </c>
     </row>
   </sheetData>
@@ -1052,27 +1089,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
